--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104724_W30.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104724_W30.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.1188</v>
+        <v>7.703</v>
       </c>
       <c r="E2" t="n">
-        <v>6.6192</v>
+        <v>6.9657</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4996</v>
+        <v>0.7373</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4966</v>
+        <v>2.4935</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.8993</v>
+        <v>-0.9015</v>
       </c>
       <c r="I2" t="n">
-        <v>3.3959</v>
+        <v>3.3949</v>
       </c>
       <c r="J2" t="n">
-        <v>3.321</v>
+        <v>3.3072</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.1029</v>
+        <v>-0.1109</v>
       </c>
       <c r="L2" t="n">
-        <v>3.4239</v>
+        <v>3.4181</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.8244</v>
+        <v>-0.8138</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.7965</v>
+        <v>-0.7906</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.0279</v>
+        <v>-0.0232</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6746</v>
+        <v>-0.0801</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0221</v>
+        <v>-0.6506999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3475</v>
+        <v>0.5707</v>
       </c>
       <c r="V2" t="n">
-        <v>5.2968</v>
+        <v>5.2896</v>
       </c>
       <c r="W2" t="n">
-        <v>5.4563</v>
+        <v>5.4474</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.1774</v>
+        <v>5.4932</v>
       </c>
       <c r="E3" t="n">
-        <v>4.5355</v>
+        <v>4.1192</v>
       </c>
       <c r="F3" t="n">
-        <v>1.642</v>
+        <v>1.374</v>
       </c>
       <c r="G3" t="n">
-        <v>3.8343</v>
+        <v>3.8312</v>
       </c>
       <c r="H3" t="n">
-        <v>3.1286</v>
+        <v>3.125</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7057</v>
+        <v>0.7062</v>
       </c>
       <c r="J3" t="n">
-        <v>2.805</v>
+        <v>2.7979</v>
       </c>
       <c r="K3" t="n">
-        <v>2.7304</v>
+        <v>2.7234</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M3" t="n">
-        <v>1.0293</v>
+        <v>1.0333</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3982</v>
+        <v>0.4016</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6311</v>
+        <v>0.6317</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2072</v>
+        <v>0.5239</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4798</v>
+        <v>0.0741</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7274</v>
+        <v>0.4498</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2507</v>
+        <v>1.2472</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2507</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0681</v>
+        <v>1.7845</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.9863</v>
+        <v>-2.2908</v>
       </c>
       <c r="F4" t="n">
-        <v>4.0544</v>
+        <v>4.0753</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0456</v>
+        <v>0.0396</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1548</v>
+        <v>0.15</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1092</v>
+        <v>-0.1104</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.4552</v>
+        <v>-1.4691</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.356</v>
+        <v>-0.3662</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.0991</v>
+        <v>-1.1029</v>
       </c>
       <c r="M4" t="n">
-        <v>1.5008</v>
+        <v>1.5087</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5109</v>
+        <v>0.5162</v>
       </c>
       <c r="O4" t="n">
-        <v>0.99</v>
+        <v>0.9925</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9782</v>
+        <v>0.6946</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1449</v>
+        <v>-0.4348</v>
       </c>
       <c r="U4" t="n">
-        <v>1.123</v>
+        <v>1.1294</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3188</v>
+        <v>-0.3155</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.3862</v>
+        <v>-0.387</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0674</v>
+        <v>0.07140000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0276</v>
+        <v>1.0134</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2964</v>
+        <v>0.7038</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7312</v>
+        <v>0.3096</v>
       </c>
       <c r="G5" t="n">
-        <v>2.3417</v>
+        <v>2.3419</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1886</v>
+        <v>1.1889</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1531</v>
+        <v>1.153</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3128</v>
+        <v>3.3033</v>
       </c>
       <c r="K5" t="n">
-        <v>2.8341</v>
+        <v>2.8268</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4787</v>
+        <v>0.4764</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9711</v>
+        <v>-0.9613</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.6455</v>
+        <v>-1.638</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6744</v>
+        <v>0.6766</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9087</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4053</v>
+        <v>-0.418</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7445000000000001</v>
+        <v>-0.3232</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3392</v>
+        <v>-0.0948</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7037</v>
+        <v>0.9881</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.6478</v>
+        <v>-2.2904</v>
       </c>
       <c r="F6" t="n">
-        <v>3.3515</v>
+        <v>3.2786</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8247</v>
+        <v>0.8241000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.136</v>
+        <v>-0.1351</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9607</v>
+        <v>0.9592000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.3005</v>
+        <v>-0.311</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2022</v>
+        <v>0.1961</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5026</v>
+        <v>-0.5071</v>
       </c>
       <c r="M6" t="n">
-        <v>1.1251</v>
+        <v>1.1351</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3382</v>
+        <v>-0.3312</v>
       </c>
       <c r="O6" t="n">
-        <v>1.4633</v>
+        <v>1.4663</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1888</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.2114</v>
+        <v>-0.8413</v>
       </c>
       <c r="U6" t="n">
-        <v>1.0226</v>
+        <v>0.9355</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="7">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6864</v>
+        <v>0.5754</v>
       </c>
       <c r="E7" t="n">
-        <v>2.1642</v>
+        <v>1.9201</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.4778</v>
+        <v>-1.3447</v>
       </c>
       <c r="G7" t="n">
-        <v>1.4578</v>
+        <v>1.4594</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.0001</v>
+        <v>-0.9969</v>
       </c>
       <c r="I7" t="n">
-        <v>2.4579</v>
+        <v>2.4563</v>
       </c>
       <c r="J7" t="n">
-        <v>2.9971</v>
+        <v>2.9934</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0518</v>
+        <v>0.0517</v>
       </c>
       <c r="L7" t="n">
-        <v>2.9452</v>
+        <v>2.9417</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.5392</v>
+        <v>-1.534</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.0519</v>
+        <v>-1.0487</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4873</v>
+        <v>-0.4854</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.4544</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2286</v>
+        <v>0.116</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3031</v>
+        <v>0.0648</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0745</v>
+        <v>0.0512</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5456</v>
+        <v>-0.5447</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5456</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. KRUTWIG</t>
+          <t>D. GARCIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1254</v>
+        <v>0.0304</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8257</v>
+        <v>-2.8277</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7002</v>
+        <v>2.858</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7266</v>
+        <v>1.1229</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0834</v>
+        <v>0.2292</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6431</v>
+        <v>0.8937</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5088</v>
+        <v>-0.4134</v>
       </c>
       <c r="K8" t="n">
-        <v>1.2105</v>
+        <v>-0.1002</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2983</v>
+        <v>-0.3132</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7822</v>
+        <v>1.5363</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1271</v>
+        <v>0.3294</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3449</v>
+        <v>1.2069</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1359</v>
+        <v>-2.2763</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1359</v>
+        <v>1.3658</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0555</v>
+        <v>-0.0242</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2522</v>
+        <v>-0.6112</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1967</v>
+        <v>0.587</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5456</v>
+        <v>-0.1578</v>
       </c>
       <c r="W8" t="n">
-        <v>0.705</v>
+        <v>0.4733</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2507</v>
+        <v>-0.6311</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. JIMENEZ</t>
+          <t>C. KRUTWIG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2125</v>
+        <v>-0.0354</v>
       </c>
       <c r="E9" t="n">
-        <v>1.0374</v>
+        <v>0.5198</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2499</v>
+        <v>-0.5552</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3758</v>
+        <v>0.7252999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1315</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5073</v>
+        <v>0.6471</v>
       </c>
       <c r="J9" t="n">
-        <v>1.4538</v>
+        <v>1.497</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0864</v>
+        <v>1.1991</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3674</v>
+        <v>0.2979</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.078</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2179</v>
+        <v>-1.1209</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8601</v>
+        <v>0.3492</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6816</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6816</v>
+        <v>1.1382</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1786</v>
+        <v>-0.2159</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4164</v>
+        <v>-0.5415</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2378</v>
+        <v>0.3256</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0913</v>
+        <v>-0.5447</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.7025</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0913</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. GARCIA</t>
+          <t>M. JIMENEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5116000000000001</v>
+        <v>-0.1232</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.0659</v>
+        <v>1.1488</v>
       </c>
       <c r="F10" t="n">
-        <v>2.5543</v>
+        <v>-1.272</v>
       </c>
       <c r="G10" t="n">
-        <v>1.1201</v>
+        <v>0.3752</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2254</v>
+        <v>-0.1295</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8948</v>
+        <v>0.5047</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4079</v>
+        <v>1.4486</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.0977</v>
+        <v>0.0862</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.3102</v>
+        <v>1.3624</v>
       </c>
       <c r="M10" t="n">
-        <v>1.528</v>
+        <v>-1.0734</v>
       </c>
       <c r="N10" t="n">
-        <v>0.323</v>
+        <v>-0.2157</v>
       </c>
       <c r="O10" t="n">
-        <v>1.205</v>
+        <v>-0.8578</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9087</v>
+        <v>0.6829</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.2719</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3631</v>
+        <v>0.6829</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5636</v>
+        <v>-0.09180000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8643999999999999</v>
+        <v>-0.2998</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3008</v>
+        <v>0.208</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1594</v>
+        <v>-1.0895</v>
       </c>
       <c r="W10" t="n">
-        <v>0.4782</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6375999999999999</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.1609</v>
+        <v>-0.7982</v>
       </c>
       <c r="E11" t="n">
-        <v>1.3265</v>
+        <v>1.5531</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.4875</v>
+        <v>-2.3513</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8252</v>
+        <v>0.8255</v>
       </c>
       <c r="H11" t="n">
-        <v>0.266</v>
+        <v>0.2669</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5592</v>
+        <v>0.5586</v>
       </c>
       <c r="J11" t="n">
-        <v>2.8095</v>
+        <v>2.8029</v>
       </c>
       <c r="K11" t="n">
-        <v>1.1751</v>
+        <v>1.1721</v>
       </c>
       <c r="L11" t="n">
-        <v>1.6344</v>
+        <v>1.6308</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.9843</v>
+        <v>-1.9774</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9092</v>
+        <v>-0.9052</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.0752</v>
+        <v>-1.0722</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6677</v>
+        <v>-0.3066</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.347</v>
+        <v>-0.1116</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3206</v>
+        <v>-0.195</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
@@ -1345,40 +1345,40 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.153</v>
+        <v>-2.1579</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.9798</v>
+        <v>-0.8631</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1731</v>
+        <v>-1.2948</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.0507</v>
+        <v>-2.0487</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.674</v>
+        <v>-0.6722</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.3767</v>
+        <v>-1.3765</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.7716</v>
+        <v>-0.7724</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.7889</v>
+        <v>-0.7896</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.2791</v>
+        <v>-1.2763</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6913</v>
+        <v>-0.6895</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5878</v>
+        <v>-0.5868</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1023</v>
+        <v>-0.1092</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2082</v>
+        <v>-0.0907</v>
       </c>
       <c r="U12" t="n">
-        <v>0.106</v>
+        <v>-0.0185</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.7793</v>
+        <v>-2.6821</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.5732</v>
+        <v>-1.576</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.2061</v>
+        <v>-1.1061</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.3858</v>
+        <v>-2.3839</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.3419</v>
+        <v>-1.3412</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.0439</v>
+        <v>-1.0426</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.365</v>
+        <v>-1.3669</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.6506999999999999</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.7143</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.0208</v>
+        <v>-1.0169</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6913</v>
+        <v>-0.6895</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.3295</v>
+        <v>-0.3275</v>
       </c>
       <c r="P13" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4613</v>
+        <v>-0.3681</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2082</v>
+        <v>-0.2091</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2531</v>
+        <v>-0.159</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="14">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>11.0901</v>
+        <v>11.7912</v>
       </c>
       <c r="E14" t="n">
-        <v>6.5519</v>
+        <v>7.082500000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>4.538400000000001</v>
+        <v>4.7087</v>
       </c>
       <c r="G14" t="n">
-        <v>9.611900000000002</v>
+        <v>9.605999999999998</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8640000000000005</v>
+        <v>0.8619000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>8.747900000000001</v>
+        <v>8.744200000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>13.9078</v>
+        <v>13.8175</v>
       </c>
       <c r="K14" t="n">
-        <v>7.1005</v>
+        <v>7.043600000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>6.807399999999999</v>
+        <v>6.7738</v>
       </c>
       <c r="M14" t="n">
-        <v>-4.2959</v>
+        <v>-4.211399999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>-6.2368</v>
+        <v>-6.182099999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>1.9409</v>
+        <v>1.9703</v>
       </c>
       <c r="P14" t="n">
-        <v>1.136</v>
+        <v>1.1382</v>
       </c>
       <c r="Q14" t="n">
-        <v>-10.2233</v>
+        <v>-10.2436</v>
       </c>
       <c r="R14" t="n">
-        <v>11.3592</v>
+        <v>11.3817</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8836999999999998</v>
+        <v>-0.1852</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.6364</v>
+        <v>-3.975</v>
       </c>
       <c r="U14" t="n">
-        <v>3.7528</v>
+        <v>3.7899</v>
       </c>
       <c r="V14" t="n">
-        <v>1.226</v>
+        <v>1.232300000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>7.504</v>
+        <v>7.4834</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.277999999999999</v>
+        <v>-6.2512</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T. HLINASON</t>
+          <t>M. PANTZAR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.3097</v>
+        <v>2.893</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5383</v>
+        <v>3.1744</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7714</v>
+        <v>-0.2814</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.2272</v>
+        <v>1.4891</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.136</v>
+        <v>2.4071</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0912</v>
+        <v>-0.918</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7579</v>
+        <v>3.549</v>
       </c>
       <c r="K15" t="n">
-        <v>0.7206</v>
+        <v>2.5371</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0373</v>
+        <v>1.012</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.9851</v>
+        <v>-2.0599</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8566</v>
+        <v>-0.13</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1285</v>
+        <v>-1.93</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1359</v>
+        <v>0.9105</v>
       </c>
       <c r="S15" t="n">
-        <v>3.2181</v>
+        <v>0.2265</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2787</v>
+        <v>-0.6415</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9393</v>
+        <v>0.868</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3188</v>
+        <v>1.405</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6375999999999999</v>
+        <v>1.405</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.3188</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. PANTZAR</t>
+          <t>T. HLINASON</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.7119</v>
+        <v>1.1601</v>
       </c>
       <c r="E16" t="n">
-        <v>2.7299</v>
+        <v>0.2682</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.018</v>
+        <v>0.8919</v>
       </c>
       <c r="G16" t="n">
-        <v>1.4957</v>
+        <v>-0.2225</v>
       </c>
       <c r="H16" t="n">
-        <v>2.4111</v>
+        <v>-0.1351</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.9154</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>3.5663</v>
+        <v>0.7504999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>2.5464</v>
+        <v>0.7131999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>1.0199</v>
+        <v>0.0372</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.0706</v>
+        <v>-0.9729</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1353</v>
+        <v>-0.8483000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.9353</v>
+        <v>-0.1246</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.2272</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9087</v>
+        <v>1.1382</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0333</v>
+        <v>1.0671</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1105</v>
+        <v>0.0249</v>
       </c>
       <c r="U16" t="n">
-        <v>1.1438</v>
+        <v>1.0423</v>
       </c>
       <c r="V16" t="n">
-        <v>1.4101</v>
+        <v>0.3155</v>
       </c>
       <c r="W16" t="n">
-        <v>1.4101</v>
+        <v>0.6311</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="17">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0662</v>
+        <v>1.0579</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7442</v>
+        <v>1.9669</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.678</v>
+        <v>-0.909</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9596</v>
+        <v>0.9629</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8618</v>
+        <v>-0.859</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8215</v>
+        <v>1.822</v>
       </c>
       <c r="J17" t="n">
-        <v>1.7429</v>
+        <v>1.7375</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4381</v>
+        <v>0.4342</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3048</v>
+        <v>1.3033</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7833</v>
+        <v>-0.7745</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.2999</v>
+        <v>-1.2932</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5165999999999999</v>
+        <v>0.5187</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.4544</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9472</v>
+        <v>0.9372</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1134</v>
+        <v>0.1204</v>
       </c>
       <c r="U17" t="n">
-        <v>1.0606</v>
+        <v>0.8168</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3862</v>
+        <v>-0.387</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2507</v>
+        <v>1.2472</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.6369</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="18">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8091</v>
+        <v>-0.1764</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3444</v>
+        <v>0.8133</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1536</v>
+        <v>-0.9898</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.2288</v>
+        <v>-1.2275</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8017</v>
+        <v>0.8013</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.0305</v>
+        <v>-2.0288</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5526</v>
+        <v>0.5486</v>
       </c>
       <c r="K18" t="n">
-        <v>1.1924</v>
+        <v>1.1893</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6398</v>
+        <v>-0.6407</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.7814</v>
+        <v>-1.7761</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3907</v>
+        <v>-0.3881</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.3907</v>
+        <v>-1.3881</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2619</v>
+        <v>0.3681</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2082</v>
+        <v>0.2647</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0537</v>
+        <v>0.1035</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1347</v>
+        <v>-1.8889</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1288</v>
+        <v>-0.4906</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0059</v>
+        <v>-1.3984</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.604</v>
+        <v>-1.6011</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2314</v>
+        <v>0.2325</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.8354</v>
+        <v>-1.8336</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0196</v>
+        <v>0.0171</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6221</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6025</v>
+        <v>-0.6035</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.6237</v>
+        <v>-1.6182</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3907</v>
+        <v>-0.3881</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.2329</v>
+        <v>-1.2301</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S19" t="n">
-        <v>1.4015</v>
+        <v>0.6423</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4419</v>
+        <v>0.0858</v>
       </c>
       <c r="U19" t="n">
-        <v>0.9597</v>
+        <v>0.5565</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.705</v>
+        <v>-0.7025</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5456</v>
+        <v>0.5447</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2507</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="20">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7114</v>
+        <v>-1.9316</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2453</v>
+        <v>0.7507</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.9567</v>
+        <v>-2.6823</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2576</v>
+        <v>0.2601</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9054</v>
+        <v>0.9046999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6478</v>
+        <v>-0.6446</v>
       </c>
       <c r="J20" t="n">
-        <v>2.4287</v>
+        <v>2.4214</v>
       </c>
       <c r="K20" t="n">
-        <v>1.1984</v>
+        <v>1.1926</v>
       </c>
       <c r="L20" t="n">
-        <v>1.2303</v>
+        <v>1.2288</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.1711</v>
+        <v>-2.1613</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2931</v>
+        <v>-0.2879</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.878</v>
+        <v>-1.8734</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.9087</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S20" t="n">
-        <v>0.031</v>
+        <v>-0.1917</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3216</v>
+        <v>-0.7994</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3526</v>
+        <v>0.6077</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
       <c r="W20" t="n">
-        <v>1.4101</v>
+        <v>1.405</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.5013</v>
+        <v>-2.4945</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.9776</v>
+        <v>-2.2446</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7457</v>
+        <v>-0.5306</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.2319</v>
+        <v>-1.7141</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.6038</v>
+        <v>-1.607</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2983</v>
+        <v>-0.2986</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.3055</v>
+        <v>-1.3083</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3401</v>
+        <v>0.3268</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5132</v>
+        <v>0.5064</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.1731</v>
+        <v>-0.1796</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.9439</v>
+        <v>-1.9337</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8115</v>
+        <v>-0.805</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.1324</v>
+        <v>-1.1287</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3738</v>
+        <v>-0.6377</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0411</v>
+        <v>-0.8087</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3327</v>
+        <v>0.171</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7131</v>
+        <v>-2.3334</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.8257</v>
+        <v>-2.2469</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8874</v>
+        <v>-0.0864</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.4169</v>
+        <v>-2.4156</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.7026</v>
+        <v>-1.7004</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7143</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.5764</v>
+        <v>-1.5845</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.4027</v>
+        <v>-0.4072</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.1737</v>
+        <v>-1.1773</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.8405</v>
+        <v>-0.831</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.2999</v>
+        <v>-1.2932</v>
       </c>
       <c r="O22" t="n">
-        <v>0.4594</v>
+        <v>0.4622</v>
       </c>
       <c r="P22" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3409</v>
+        <v>0.0335</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.2493</v>
+        <v>-0.6624</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0916</v>
+        <v>0.6959</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="23">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.7805</v>
+        <v>-2.5676</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.4155</v>
+        <v>-2.7166</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.365</v>
+        <v>0.149</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.4736</v>
+        <v>-3.4706</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.9603</v>
+        <v>-2.9582</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.5133</v>
+        <v>-0.5123</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.217</v>
+        <v>-2.2223</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.5026</v>
+        <v>-1.5071</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.7143</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.2566</v>
+        <v>-1.2483</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.4577</v>
+        <v>-1.4511</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2011</v>
+        <v>0.2028</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9888</v>
+        <v>0.2217</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9717</v>
+        <v>-0.2652</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0171</v>
+        <v>0.4868</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.2268</v>
+        <v>-0.2292</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.2268</v>
+        <v>-0.2292</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.0515</v>
+        <v>-3.4834</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.0248</v>
+        <v>-5.6976</v>
       </c>
       <c r="F24" t="n">
-        <v>1.9733</v>
+        <v>2.2142</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.7705</v>
+        <v>-1.7739</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7453</v>
+        <v>0.744</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.5158</v>
+        <v>-2.5179</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.3189</v>
+        <v>-1.3325</v>
       </c>
       <c r="K24" t="n">
-        <v>0.9107</v>
+        <v>0.9028</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.2296</v>
+        <v>-2.2353</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.4516</v>
+        <v>-0.4414</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.1654</v>
+        <v>-0.1588</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.2863</v>
+        <v>-0.2826</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.0447</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.4078</v>
+        <v>-3.4145</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.782</v>
+        <v>-0.2056</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.4575</v>
+        <v>-1.1084</v>
       </c>
       <c r="U24" t="n">
-        <v>0.6756</v>
+        <v>0.9028</v>
       </c>
       <c r="V24" t="n">
-        <v>0.5456</v>
+        <v>0.5447</v>
       </c>
       <c r="W24" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="X24" t="n">
-        <v>0.3862</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-11.0901</v>
+        <v>-9.514900000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.538399999999999</v>
+        <v>-4.708800000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-6.5518</v>
+        <v>-4.806299999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>-9.6119</v>
+        <v>-9.6061</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.8641</v>
+        <v>-0.8617000000000004</v>
       </c>
       <c r="I25" t="n">
-        <v>-8.7477</v>
+        <v>-8.7441</v>
       </c>
       <c r="J25" t="n">
-        <v>4.295799999999999</v>
+        <v>4.211600000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>6.2366</v>
+        <v>6.1818</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.9407</v>
+        <v>-1.9703</v>
       </c>
       <c r="M25" t="n">
-        <v>-13.9078</v>
+        <v>-13.8173</v>
       </c>
       <c r="N25" t="n">
-        <v>-7.1008</v>
+        <v>-7.0437</v>
       </c>
       <c r="O25" t="n">
-        <v>-6.806999999999999</v>
+        <v>-6.7738</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.136</v>
+        <v>-1.1381</v>
       </c>
       <c r="Q25" t="n">
-        <v>-11.3592</v>
+        <v>-11.3818</v>
       </c>
       <c r="R25" t="n">
-        <v>10.2232</v>
+        <v>10.2435</v>
       </c>
       <c r="S25" t="n">
-        <v>0.8837000000000006</v>
+        <v>2.4614</v>
       </c>
       <c r="T25" t="n">
-        <v>-3.7527</v>
+        <v>-3.7898</v>
       </c>
       <c r="U25" t="n">
-        <v>4.6365</v>
+        <v>6.251300000000001</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.2261</v>
+        <v>-1.2325</v>
       </c>
       <c r="W25" t="n">
-        <v>6.278</v>
+        <v>6.251100000000001</v>
       </c>
       <c r="X25" t="n">
-        <v>-7.5041</v>
+        <v>-7.4834</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104724_W30.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104724_W30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104724_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104724_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0.07140000000000001</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104724_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104724_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104724_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104724_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.6311</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104724_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104724_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104724_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104724_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104724_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104724_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-6.2512</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104724_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104724_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104724_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104724_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104724_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-2.4945</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104724_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104724_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104724_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104724_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104724_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-7.4834</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
